--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,87; 50,64</t>
+          <t>38,66; 50,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,54; 69,34</t>
+          <t>56,91; 69,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,47; 53,34</t>
+          <t>38,82; 52,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,52</t>
+          <t>5,0; 9,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,3; 60,86</t>
+          <t>47,5; 60,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,22; 86,01</t>
+          <t>73,06; 85,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,14; 78,64</t>
+          <t>65,87; 78,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,6</t>
+          <t>9,31; 14,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,69; 52,98</t>
+          <t>44,3; 53,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,38; 75,14</t>
+          <t>65,86; 74,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,8; 63,29</t>
+          <t>54,19; 64,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,92</t>
+          <t>7,53; 11,01</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,47; 55,89</t>
+          <t>40,68; 56,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,67; 64,87</t>
+          <t>52,32; 65,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,85; 55,87</t>
+          <t>42,84; 56,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,31</t>
+          <t>4,12; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,64; 71,62</t>
+          <t>58,77; 71,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,47; 88,44</t>
+          <t>78,02; 88,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,68; 76,41</t>
+          <t>64,78; 76,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 15,01</t>
+          <t>9,61; 15,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 62,15</t>
+          <t>52,35; 62,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,85; 74,72</t>
+          <t>65,89; 75,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,27; 65,16</t>
+          <t>56,16; 64,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,7</t>
+          <t>7,12; 10,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,42; 44,92</t>
+          <t>34,34; 44,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,42; 54,67</t>
+          <t>44,27; 54,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,13; 51,5</t>
+          <t>40,69; 51,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,44</t>
+          <t>2,64; 11,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,22; 65,22</t>
+          <t>47,08; 65,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 65,93</t>
+          <t>52,49; 66,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 57,94</t>
+          <t>38,43; 57,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,63</t>
+          <t>6,63; 14,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,52; 48,47</t>
+          <t>39,03; 48,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,14; 56,76</t>
+          <t>48,31; 56,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,05; 51,22</t>
+          <t>41,89; 51,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,13</t>
+          <t>2,82; 10,99</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 37,76</t>
+          <t>31,31; 37,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,54; 51,0</t>
+          <t>43,75; 50,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,83; 49,68</t>
+          <t>42,19; 49,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,27</t>
+          <t>8,39; 12,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,45; 60,76</t>
+          <t>52,05; 61,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,37; 81,69</t>
+          <t>73,7; 81,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,96; 67,04</t>
+          <t>58,41; 66,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 64,13</t>
+          <t>11,69; 58,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,14; 45,63</t>
+          <t>39,91; 45,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,76; 62,31</t>
+          <t>56,58; 62,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,13; 56,04</t>
+          <t>50,44; 56,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 42,35</t>
+          <t>10,86; 46,58</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,3; 41,05</t>
+          <t>27,02; 40,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 51,74</t>
+          <t>39,94; 50,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,74; 46,04</t>
+          <t>36,08; 46,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,55</t>
+          <t>5,73; 10,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 54,22</t>
+          <t>43,67; 53,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,25; 65,82</t>
+          <t>57,83; 65,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,66; 57,23</t>
+          <t>47,97; 56,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 14,78</t>
+          <t>8,96; 14,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,91; 48,38</t>
+          <t>39,78; 47,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,67; 59,17</t>
+          <t>52,57; 59,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,29; 51,4</t>
+          <t>44,67; 51,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,49</t>
+          <t>8,65; 12,49</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 23,31</t>
+          <t>8,95; 22,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,63</t>
+          <t>10,49; 25,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,45; 35,09</t>
+          <t>16,55; 34,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,2</t>
+          <t>1,23; 8,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,64; 33,55</t>
+          <t>27,69; 33,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,76; 43,05</t>
+          <t>35,77; 42,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,22; 33,13</t>
+          <t>26,31; 33,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 14,82</t>
+          <t>10,17; 14,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 31,87</t>
+          <t>25,92; 31,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,44; 39,93</t>
+          <t>33,43; 40,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,15; 32,5</t>
+          <t>26,21; 32,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,26</t>
+          <t>8,51; 12,33</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,58; 39,04</t>
+          <t>34,78; 39,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,56</t>
+          <t>47,11; 51,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,83; 46,51</t>
+          <t>41,99; 46,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,79</t>
+          <t>6,07; 8,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,92; 48,3</t>
+          <t>44,02; 48,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,48; 63,61</t>
+          <t>59,73; 63,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,15; 53,36</t>
+          <t>49,24; 53,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 32,24</t>
+          <t>11,66; 32,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,4; 43,45</t>
+          <t>40,42; 43,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54,47; 57,62</t>
+          <t>54,58; 57,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,44; 49,64</t>
+          <t>46,39; 49,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 21,36</t>
+          <t>9,6; 21,78</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109535; 142688</t>
+          <t>108945; 143390</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144306; 176972</t>
+          <t>145246; 178065</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86488; 116902</t>
+          <t>85073; 115230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24457; 48106</t>
+          <t>25278; 48499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97603; 125581</t>
+          <t>98026; 125846</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151403; 177866</t>
+          <t>151087; 176539</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>136730; 162567</t>
+          <t>136168; 162964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41576; 65313</t>
+          <t>41648; 63540</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>213272; 258614</t>
+          <t>216249; 262390</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>306685; 347135</t>
+          <t>304302; 345108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>229099; 269527</t>
+          <t>230790; 273144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71389; 104017</t>
+          <t>71774; 104868</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79534; 109840</t>
+          <t>79936; 111103</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139654; 175332</t>
+          <t>141402; 177729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98014; 127810</t>
+          <t>98005; 129661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17699; 37596</t>
+          <t>18612; 38014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>131051; 160070</t>
+          <t>131347; 159436</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>186110; 209747</t>
+          <t>185038; 209007</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>157541; 186112</t>
+          <t>157775; 187212</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35473; 57406</t>
+          <t>36765; 57699</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>219826; 261028</t>
+          <t>219869; 260730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>334172; 379182</t>
+          <t>334342; 380889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265793; 307772</t>
+          <t>265242; 305402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59201; 89331</t>
+          <t>59444; 88420</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116784; 152374</t>
+          <t>116500; 150847</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>181648; 223570</t>
+          <t>181046; 223247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132613; 170201</t>
+          <t>134462; 169962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14123; 76461</t>
+          <t>17614; 78027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59542; 82246</t>
+          <t>59368; 82282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95807; 120610</t>
+          <t>96010; 121377</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48410; 70991</t>
+          <t>47085; 69998</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10710; 22756</t>
+          <t>11068; 24602</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183930; 225577</t>
+          <t>181625; 225691</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>284896; 335935</t>
+          <t>285940; 336377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190506; 232051</t>
+          <t>189758; 233306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24795; 92955</t>
+          <t>23541; 91806</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238562; 293280</t>
+          <t>243145; 294418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>339481; 397644</t>
+          <t>341149; 395780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>266390; 316341</t>
+          <t>268664; 316917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86013; 127016</t>
+          <t>86770; 128144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>241791; 285554</t>
+          <t>244615; 287352</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>387984; 426187</t>
+          <t>384482; 422799</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>302908; 350328</t>
+          <t>305253; 348446</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>115051; 627293</t>
+          <t>114349; 567425</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>500338; 568826</t>
+          <t>497461; 564099</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>738720; 810856</t>
+          <t>736295; 809740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>581203; 649718</t>
+          <t>584833; 651047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>214710; 852494</t>
+          <t>218670; 937526</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56562; 85055</t>
+          <t>55984; 83095</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>129530; 165760</t>
+          <t>127939; 162768</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134302; 172995</t>
+          <t>135569; 172904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26476; 50141</t>
+          <t>27201; 50501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>177454; 219987</t>
+          <t>177166; 218599</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>335449; 385665</t>
+          <t>338877; 385903</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>238342; 286174</t>
+          <t>239860; 284983</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76532; 124376</t>
+          <t>75344; 124621</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244604; 296555</t>
+          <t>243841; 294026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>477368; 536293</t>
+          <t>476419; 539260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>387920; 450178</t>
+          <t>391190; 448800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113431; 164350</t>
+          <t>113867; 164480</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9596; 24910</t>
+          <t>9559; 23751</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10129; 26351</t>
+          <t>10783; 25951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17248; 36791</t>
+          <t>17353; 36625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3362; 19721</t>
+          <t>2952; 20518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>240094; 291412</t>
+          <t>240561; 293200</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>277243; 333762</t>
+          <t>277298; 333175</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>191308; 241735</t>
+          <t>191985; 243758</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80509; 112852</t>
+          <t>77401; 110881</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>253193; 310921</t>
+          <t>252819; 309824</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>293573; 350623</t>
+          <t>293543; 352619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>218235; 271250</t>
+          <t>218723; 273408</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85989; 122842</t>
+          <t>85214; 123568</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>659868; 744868</t>
+          <t>663650; 745626</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1006826; 1101905</t>
+          <t>1006836; 1105466</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>793044; 881641</t>
+          <t>796012; 879129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>198912; 296680</t>
+          <t>204842; 299594</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1010367; 1111121</t>
+          <t>1012598; 1108999</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1492817; 1596405</t>
+          <t>1499170; 1595396</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1142699; 1240786</t>
+          <t>1144883; 1242090</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>415848; 1153448</t>
+          <t>417253; 1164698</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1700276; 1828759</t>
+          <t>1701223; 1826901</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2531178; 2677487</t>
+          <t>2536395; 2672696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1960258; 2095273</t>
+          <t>1958200; 2092584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>666224; 1485559</t>
+          <t>667794; 1514625</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,66; 50,89</t>
+          <t>38,7; 51,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,91; 69,77</t>
+          <t>55,79; 69,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,82; 52,58</t>
+          <t>39,37; 53,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,6</t>
+          <t>5,48; 9,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,5; 60,99</t>
+          <t>46,94; 60,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,06; 85,37</t>
+          <t>73,34; 85,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,87; 78,83</t>
+          <t>66,46; 79,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 14,2</t>
+          <t>9,29; 14,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,3; 53,76</t>
+          <t>43,68; 53,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,86; 74,7</t>
+          <t>66,3; 75,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,19; 64,14</t>
+          <t>53,6; 63,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,01</t>
+          <t>7,91; 11,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,68; 56,54</t>
+          <t>40,58; 55,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,32; 65,76</t>
+          <t>52,48; 65,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 56,68</t>
+          <t>42,37; 55,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,41</t>
+          <t>4,39; 9,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,77; 71,34</t>
+          <t>58,95; 71,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,02; 88,13</t>
+          <t>78,29; 88,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,78; 76,87</t>
+          <t>65,02; 76,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 15,08</t>
+          <t>9,83; 15,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,35; 62,08</t>
+          <t>51,58; 61,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,89; 75,06</t>
+          <t>66,35; 75,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,16; 64,66</t>
+          <t>56,2; 65,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,59</t>
+          <t>7,59; 11,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,34; 44,47</t>
+          <t>33,75; 44,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,27; 54,59</t>
+          <t>44,29; 54,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,69; 51,43</t>
+          <t>40,44; 51,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,68</t>
+          <t>8,4; 14,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,08; 65,25</t>
+          <t>47,36; 64,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,49; 66,35</t>
+          <t>52,41; 66,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,43; 57,13</t>
+          <t>38,88; 58,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,74</t>
+          <t>6,6; 13,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,03; 48,5</t>
+          <t>38,99; 48,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,31; 56,83</t>
+          <t>48,35; 57,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,89; 51,5</t>
+          <t>41,48; 51,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,99</t>
+          <t>8,6; 13,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 37,91</t>
+          <t>30,79; 37,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,75; 50,76</t>
+          <t>43,5; 50,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 49,77</t>
+          <t>41,58; 49,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,38</t>
+          <t>9,42; 13,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,05; 61,14</t>
+          <t>52,01; 61,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,7; 81,04</t>
+          <t>73,93; 81,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,41; 66,68</t>
+          <t>58,49; 66,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 58,01</t>
+          <t>10,89; 15,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,91; 45,25</t>
+          <t>39,9; 45,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,58; 62,22</t>
+          <t>56,59; 62,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,44; 56,15</t>
+          <t>50,63; 56,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 46,58</t>
+          <t>10,49; 13,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,02; 40,1</t>
+          <t>27,15; 40,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,94; 50,81</t>
+          <t>40,36; 51,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,02</t>
+          <t>35,93; 46,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,63</t>
+          <t>5,68; 10,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,67; 53,88</t>
+          <t>43,68; 53,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,83; 65,86</t>
+          <t>57,74; 65,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,97; 56,99</t>
+          <t>48,19; 57,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,81</t>
+          <t>13,12; 17,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,78; 47,97</t>
+          <t>39,6; 47,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 59,5</t>
+          <t>52,8; 59,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,67; 51,24</t>
+          <t>44,24; 51,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 12,49</t>
+          <t>10,54; 13,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,95; 22,23</t>
+          <t>8,94; 22,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 25,24</t>
+          <t>10,08; 25,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 34,94</t>
+          <t>16,74; 33,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,53</t>
+          <t>1,55; 9,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,69; 33,75</t>
+          <t>27,35; 33,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,77; 42,98</t>
+          <t>35,87; 43,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,31; 33,41</t>
+          <t>26,57; 33,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,56</t>
+          <t>11,13; 15,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,92; 31,76</t>
+          <t>26,18; 31,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,43; 40,16</t>
+          <t>33,51; 40,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,21; 32,76</t>
+          <t>26,14; 32,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,51; 12,33</t>
+          <t>9,31; 13,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,78; 39,07</t>
+          <t>34,74; 39,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,72</t>
+          <t>47,28; 51,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,99; 46,37</t>
+          <t>41,72; 46,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,87</t>
+          <t>7,9; 9,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,02; 48,21</t>
+          <t>43,97; 48,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,73; 63,57</t>
+          <t>59,73; 63,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,24; 53,42</t>
+          <t>49,16; 53,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 32,55</t>
+          <t>12,02; 14,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,42; 43,41</t>
+          <t>40,46; 43,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54,58; 57,51</t>
+          <t>54,44; 57,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,39; 49,58</t>
+          <t>46,6; 49,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 21,78</t>
+          <t>10,28; 11,74</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87031</t>
+          <t>97536</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108945; 143390</t>
+          <t>109030; 144457</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145246; 178065</t>
+          <t>142379; 177610</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85073; 115230</t>
+          <t>86288; 117345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25278; 48499</t>
+          <t>30171; 54519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98026; 125846</t>
+          <t>96870; 125579</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151087; 176539</t>
+          <t>151669; 177177</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>136168; 162964</t>
+          <t>137389; 164572</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41648; 63540</t>
+          <t>45363; 69469</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216249; 262390</t>
+          <t>213229; 259757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304302; 345108</t>
+          <t>306318; 348796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>230790; 273144</t>
+          <t>228257; 272303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71774; 104868</t>
+          <t>82137; 116286</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46319</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>83903</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79936; 111103</t>
+          <t>79757; 108499</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141402; 177729</t>
+          <t>141838; 176807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98005; 129661</t>
+          <t>96920; 128008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18612; 38014</t>
+          <t>21195; 44593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>131347; 159436</t>
+          <t>131755; 159358</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>185038; 209007</t>
+          <t>185681; 209901</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>157775; 187212</t>
+          <t>158370; 186631</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36765; 57699</t>
+          <t>41579; 66008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>219869; 260730</t>
+          <t>216633; 257969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>334342; 380889</t>
+          <t>336667; 382390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265242; 305402</t>
+          <t>265434; 307954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59444; 88420</t>
+          <t>68807; 100864</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>52467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>70507</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116500; 150847</t>
+          <t>114499; 152414</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>181046; 223247</t>
+          <t>181125; 221802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134462; 169962</t>
+          <t>133633; 168575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17614; 78027</t>
+          <t>39615; 68885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59368; 82282</t>
+          <t>59721; 81782</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96010; 121377</t>
+          <t>95876; 121787</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47085; 69998</t>
+          <t>47641; 71524</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11068; 24602</t>
+          <t>12383; 25666</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181625; 225691</t>
+          <t>181445; 224450</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>285940; 336377</t>
+          <t>286166; 338691</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>189758; 233306</t>
+          <t>187906; 232484</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23541; 91806</t>
+          <t>56659; 88625</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106257</t>
+          <t>126423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>300658</t>
+          <t>110517</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>406914</t>
+          <t>236939</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>243145; 294418</t>
+          <t>239092; 291495</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>341149; 395780</t>
+          <t>339181; 394969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>268664; 316917</t>
+          <t>264768; 316800</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86770; 128144</t>
+          <t>106570; 151434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>244615; 287352</t>
+          <t>244439; 286934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>384482; 422799</t>
+          <t>385711; 425975</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>305253; 348446</t>
+          <t>305658; 348591</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>114349; 567425</t>
+          <t>93812; 129287</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>497461; 564099</t>
+          <t>497339; 567235</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>736295; 809740</t>
+          <t>736463; 808925</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>584833; 651047</t>
+          <t>586953; 652259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>218670; 937526</t>
+          <t>209032; 266452</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>43921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>102916</t>
+          <t>125400</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>140457</t>
+          <t>169321</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55984; 83095</t>
+          <t>56246; 83748</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>127939; 162768</t>
+          <t>129285; 164516</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135569; 172904</t>
+          <t>135021; 174205</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27201; 50501</t>
+          <t>32250; 58576</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>177166; 218599</t>
+          <t>177218; 216659</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>338877; 385903</t>
+          <t>338327; 385574</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>239860; 284983</t>
+          <t>240970; 289026</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75344; 124621</t>
+          <t>109012; 144855</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>243841; 294026</t>
+          <t>242739; 293485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>476419; 539260</t>
+          <t>478538; 539254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>391190; 448800</t>
+          <t>387420; 449682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113867; 164480</t>
+          <t>147375; 191575</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>109843</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>102858</t>
+          <t>120353</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9559; 23751</t>
+          <t>9552; 24449</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10783; 25951</t>
+          <t>10365; 25963</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17353; 36625</t>
+          <t>17553; 35626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2952; 20518</t>
+          <t>3670; 22879</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>240561; 293200</t>
+          <t>237590; 290896</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>277298; 333175</t>
+          <t>278094; 335390</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>191985; 243758</t>
+          <t>193879; 244974</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>77401; 110881</t>
+          <t>93935; 132082</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>252819; 309824</t>
+          <t>255374; 309393</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>293543; 352619</t>
+          <t>294255; 351668</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>218723; 273408</t>
+          <t>218172; 271868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85214; 123568</t>
+          <t>100693; 141590</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259663</t>
+          <t>305122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>612019</t>
+          <t>473438</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>871682</t>
+          <t>778560</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>663650; 745626</t>
+          <t>662830; 751903</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1006836; 1105466</t>
+          <t>1010607; 1101968</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>796012; 879129</t>
+          <t>790834; 881752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204842; 299594</t>
+          <t>272039; 342664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1012598; 1108999</t>
+          <t>1011492; 1108073</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1499170; 1595396</t>
+          <t>1499081; 1597490</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1144883; 1242090</t>
+          <t>1143067; 1239616</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>417253; 1164698</t>
+          <t>436908; 510410</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1701223; 1826901</t>
+          <t>1702672; 1828361</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2536395; 2672696</t>
+          <t>2529849; 2670020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1958200; 2092584</t>
+          <t>1967124; 2100307</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>667794; 1514625</t>
+          <t>727792; 830608</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
